--- a/artfynd/S 2722-2025 artfynd.xlsx
+++ b/artfynd/S 2722-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7235624</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7235596</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7235616</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68393166</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64038961</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/544678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103395970</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103395985</t>
         </is>
       </c>
     </row>
@@ -1642,6 +1687,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103397372</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103395986</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68393121</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/310828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/341156</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2200,6 +2270,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111818292</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2316,6 +2391,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64038928</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2413,6 +2493,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104398347</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104398348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2611,8 +2701,33 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104066119</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>